--- a/Bangalore-March-2026.xlsx
+++ b/Bangalore-March-2026.xlsx
@@ -181,22 +181,22 @@
     <t>BALENO</t>
   </si>
   <si>
-    <t>Celerio</t>
-  </si>
-  <si>
-    <t>Crysta</t>
+    <t>CELERIO</t>
+  </si>
+  <si>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>DZIRE</t>
   </si>
   <si>
-    <t>Fortuner</t>
+    <t>FORTUNER</t>
   </si>
   <si>
     <t>HYCROSS</t>
   </si>
   <si>
-    <t>MG EVS</t>
+    <t>MG ZS EV</t>
   </si>
   <si>
     <t>SWIFT</t>
